--- a/resultados/Swift_completos.xlsx
+++ b/resultados/Swift_completos.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,6 +478,816 @@
           <t>Llave</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>9473ee35-aba6-533d-8279-6e29c6e51b90</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>12001 OZEL TEKSTIL.pdf</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CHASUS33XXX</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025-02-12</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>30.449,84</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>OZEL TEKSTIL INSAAT SANAYI VE TICARET AS</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>OZEL TEKSTIL INSAAT SANAYI VE TICARET AS CHASUS33XXX</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>c1e85139-8ac3-58a4-bc7d-3775befb6c76</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>12084 BMS FASHION.pdf</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CHASUS33XXX</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2025-02-12</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>382,00</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>BMS FASHION</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>BMS FASHION CHASUS33XXX</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>771f9260-cd27-59b5-80f7-ba5f740632af</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>13284 SOORTY ENTERPRISES.pdf</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CHASUS33XXX</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>26.550,00</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>MS SOORTY ENTERPRISES PVT LTD</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>MS SOORTY ENTERPRISES PVT LTD CHASUS33XXX</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>b7443854-e5de-5a73-bdb8-c3fccf786250</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>13304 13872 13873 SHAOXING ADA.pdf</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>BOFAUS3MXXX</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>15.007,56</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SHAOXING ADA TEXTILE CO LTD</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>MIAMI</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>SHAOXING ADA TEXTILE CO LTD BOFAUS3MXXX</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>15bcec49-da59-587a-8a4f-d36127ffa799</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>13318 SEDATEX.pdf</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>PNBPUS3NNYC</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>231,00</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SEDATEX SA</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>SEDATEX SA PNBPUS3NNYC</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>90956e66-b356-5d6c-a333-ad0c51cf84be</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>13351 ARTISTIC FABRICS.pdf</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>PNBPUS3NNYC</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1.129,05</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>ARTISTIC FABRIC MILLS PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ARTISTIC FABRIC MILLS PRIVATE LIMITED PNBPUS3NNYC</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>14913956-eee0-56f5-9daa-02ae42240264</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>13373 KASSIM TEXTILES.pdf</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>PNBPUS3NNYC</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>111,60</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>KASSIM TEXTILES  PVT  LTD</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>KASSIM TEXTILES  PVT  LTD PNBPUS3NNYC</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>bbc9d498-cf5e-5440-9331-380b7ea21ba6</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>13380 13381 SHAOXING TUJIA.pdf</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>PNBPUS3NNYC</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1.923,40</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SHAOXING TUJIA IMPORT AND EXPORT CO LTD</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>SHAOXING TUJIA IMPORT AND EXPORT CO LTD PNBPUS3NNYC</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>c7794adb-8300-52d3-b652-603d7345db78</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>13520 13580 13969 YULIN YIXING.pdf</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>PNBPUS3NNYC</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>7.483,60</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>YULIN YIXING SPINNING AND WEAVING CO LTD</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>YULIN YIXING SPINNING AND WEAVING CO LTD PNBPUS3NNYC</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>d2dc14da-3916-57fb-954b-02ecac7de8c9</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>13650 BMS FASHION.pdf</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>PNBPUS3NNYC</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>21.876,48</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>BMS FASHION</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>BMS FASHION PNBPUS3NNYC</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>938f3307-ea41-5b10-b070-2ddf3ce6ca74</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>13674 13675 SHAOXING TUJIA.pdf</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>PNBPUS3NNYC</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>4.421,00</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SHAOXING TUJIA IMPORT AND EXPORT CO LTD</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>SHAOXING TUJIA IMPORT AND EXPORT CO LTD PNBPUS3NNYC</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>c00bfeb7-da88-509d-983c-ce2a8c58a6e8</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>13769 TEXTIFILIO.pdf</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>PNBPUS3NNYC</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>180,64</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>TEXTILFIO MALHAS LTDA</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>TEXTILFIO MALHAS LTDA PNBPUS3NNYC</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>c3f4779d-ccc2-5941-9eb9-590e58943037</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>14047 SHAOXING NAYING.pdf</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>PNBPUS3NNYC</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>435,60</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SHAOXING NAYING TEXTILE CO LTD</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>SHAOXING NAYING TEXTILE CO LTD PNBPUS3NNYC</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>e05bf8c2-b96f-5a86-b6ba-e458eb19839b</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>14055 14056 SHAOXING ADA.pdf</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>PNBPUS3NNYC</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1.631,78</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SHAOXING ADA TEXTILE CO LTD</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>SHAOXING ADA TEXTILE CO LTD PNBPUS3NNYC</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>f8f4245b-dc41-5ae3-881b-5640578f31e8</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>14059 14060 SHAOXING JINZHOU.pdf</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>PNBPUS3NNYC</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1.113,60</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SHAOXING JINZHOU TEXTILE TECHNOLOGY CO LTD</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>SHAOXING JINZHOU TEXTILE TECHNOLOGY CO LTD PNBPUS3NNYC</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -490,7 +1300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -555,6 +1365,654 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>6d4c062c-93cd-5692-be13-ebd78ae614d5</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>13301 AKBASLAR TEKSTIL.pdf</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>BKTRUS33XXX</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>14955.42</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>AKBASLAR TEKSTIL ENERJI SANAYI VE TICARET A S</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>AKBASLAR TEKSTIL ENERJI SANAYI VE TICARET A S BKTRUS33XXX</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>e1639fb7-6c0c-53ad-ac34-833f012b257e</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>13309 TEXTIL CANATIBA.pdf</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>BKTRUS33XXX</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>118.49</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>TEXTIL CANATIBA LTDA</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>TEXTIL CANATIBA LTDA BKTRUS33XXX</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>03658ad5-bb7d-5c35-895b-d00afc45c353</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>13418 ARTISTIC FABRIC MILLS.pdf</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>BKTRUS33XXX</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>829.45</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ARTISTIC FABRIC MILLS PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ARTISTIC FABRIC MILLS PRIVATE LIMITED BKTRUS33XXX</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>aac99980-43fd-5bf5-8c9b-84c380d38030</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>13429 13671 13830 SEDATEX.pdf</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>BKTRUS33XXX</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>804.93</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SEDATEX SA</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>SEDATEX SA BKTRUS33XXX</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1ec5b59d-f7f9-511d-b205-9099968075a7</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>13498 13602 14249 14254 14255 14256 14258 14314 14315 SHAOXING TUJIA.pdf</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>BKTRUS33XXX</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>42868.33</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SHAOXING TUJIA IMPORT AND EXPORT CO LTD</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>SHAOXING TUJIA IMPORT AND EXPORT CO LTD BKTRUS33XXX</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>168531ec-7009-506c-9c6a-f43bad519e30</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>13510 SHANGHAI DAYA.pdf</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>BKTRUS33XXX</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>17307.57</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SHANGHAI DAYA IMPORT AND EXPORT CO LTD</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>SHANGHAI DAYA IMPORT AND EXPORT CO LTD BKTRUS33XXX</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>fdaddcf2-08be-5ad0-82d7-f4481ac217e0</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>13538 SHAOXING JINZHOU.pdf</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>PNBPUS3NNYC</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>13556.12</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SHAOXING JINZHOU TEXTILE TECHNOLOGY CO LTD</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>SHAOXING JINZHOU TEXTILE TECHNOLOGY CO LTD PNBPUS3NNYC</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>6233e4ef-c9f6-561d-80ee-005d06569445</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>13540 14295 14296 14297 14298 14299 14300 14301 14302 14303 14304 WUJIANG LA MODE.pdf</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BKTRUS33XXX</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>34184.77</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>WUJIANG LA MODE TEXTILE CO LTD</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>WUJIANG LA MODE TEXTILE CO LTD BKTRUS33XXX</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>16fea88e-4b36-5996-8567-06a50cd52050</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>13572 PROSPERITY TEXTILE.pdf</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>PNBPUS3NNYC</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>8831.40</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>PROSPERITY TEXTILE H K LTD</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>PROSPERITY TEXTILE H K LTD PNBPUS3NNYC</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>eb76812b-75d5-5761-ad89-7cafa5fb33f5</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>13718 TUSA DIS TICARET.pdf</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BKTRUS33XXX</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>123.50</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>TUSA DIS TICARET AS</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>TUSA DIS TICARET AS BKTRUS33XXX</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>921e6c86-71ae-5ee5-a064-fa2898b42987</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>13926 14094 GID LLC.pdf</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CHASUS33XXX</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>189260.60</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>GID LLC</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>GID LLC CHASUS33XXX</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>d6535733-1793-5e7f-8a16-66ffe6cf0a26</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>14161 14289 14290 SHAOXING NAYING.pdf</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>BKTRUS33XXX</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>795.80</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SHAOXING NAYING TEXTILE CO LTD</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ESTADOS UNIDOS</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>NUEVA YORK</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>SHAOXING NAYING TEXTILE CO LTD BKTRUS33XXX</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resultados/Swift_completos.xlsx
+++ b/resultados/Swift_completos.xlsx
@@ -7904,7 +7904,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>8035</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>artistic-fabric-mills-private-limited-pnbpus3nnyc-4b99a154</t>
@@ -14840,7 +14844,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>8132</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>gid-llc-chasus33xxx-fd5d657c</t>
@@ -21546,7 +21554,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>10086</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>shaoxing-ada-textile-co-ltd-bofaus3mxxx-fbdbfae5</t>
@@ -24068,7 +24080,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>9101</t>
+        </is>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
           <t>ozel-tekstil-insaat-sanayi-ve-ticaret-pnbpus3nnyc-3bec9adb</t>
@@ -25052,7 +25068,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K399" t="inlineStr"/>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>4019</t>
+        </is>
+      </c>
       <c r="L399" t="inlineStr">
         <is>
           <t>prosperity-textile-h-k-ltd-bktrus33xxx-46b27ee9</t>
@@ -25234,7 +25254,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K402" t="inlineStr"/>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>4017</t>
+        </is>
+      </c>
       <c r="L402" t="inlineStr">
         <is>
           <t>raymond-uco-denim-private-limited-chasus33xxx-392a2c18</t>
@@ -25292,7 +25316,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K403" t="inlineStr"/>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>5022</t>
+        </is>
+      </c>
       <c r="L403" t="inlineStr">
         <is>
           <t>raymond-uco-denim-private-limited-chasus33xxx-392a2c18</t>
@@ -25970,7 +25998,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K414" t="inlineStr"/>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>4043</t>
+        </is>
+      </c>
       <c r="L414" t="inlineStr">
         <is>
           <t>kipas-pazarlama-ve-ticaret-as-bktrus33xxx-90661b18</t>
@@ -26028,7 +26060,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K415" t="inlineStr"/>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>5024</t>
+        </is>
+      </c>
       <c r="L415" t="inlineStr"/>
     </row>
     <row r="416">
@@ -28298,7 +28334,11 @@
           <t>Completo</t>
         </is>
       </c>
-      <c r="K452" t="inlineStr"/>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>9075</t>
+        </is>
+      </c>
       <c r="L452" t="inlineStr">
         <is>
           <t>ozel-tekstil-insaat-sanayi-ve-ticaret-pnbpus3nnyc-3bec9adb</t>
